--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/VIRGINIA_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/VIRGINIA_2021.xlsx
@@ -2004,7 +2004,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C92">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C199">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C208">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C556">
